--- a/results/full_text_comparison.xlsx
+++ b/results/full_text_comparison.xlsx
@@ -11,6 +11,10 @@
     <sheet name="Full" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="Full1" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="Full2" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Full3" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Full4" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Full5" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="Full6" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="0" fullCalcOnLoad="1"/>
@@ -1700,4 +1704,871 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:U3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="3" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
+      <c r="B1" s="3" t="inlineStr">
+        <is>
+          <t>binary_metrics.accuracy</t>
+        </is>
+      </c>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>binary_metrics.precision</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>binary_metrics.recall</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>binary_metrics.f1</t>
+        </is>
+      </c>
+      <c r="F1" s="3" t="inlineStr">
+        <is>
+          <t>category_metrics.accuracy</t>
+        </is>
+      </c>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>category_metrics.precision_macro</t>
+        </is>
+      </c>
+      <c r="H1" s="3" t="inlineStr">
+        <is>
+          <t>category_metrics.recall_macro</t>
+        </is>
+      </c>
+      <c r="I1" s="3" t="inlineStr">
+        <is>
+          <t>category_metrics.f1_macro</t>
+        </is>
+      </c>
+      <c r="J1" s="3" t="inlineStr">
+        <is>
+          <t>category_metrics.precision_weighted</t>
+        </is>
+      </c>
+      <c r="K1" s="3" t="inlineStr">
+        <is>
+          <t>category_metrics.recall_weighted</t>
+        </is>
+      </c>
+      <c r="L1" s="3" t="inlineStr">
+        <is>
+          <t>category_metrics.f1_weighted</t>
+        </is>
+      </c>
+      <c r="M1" s="3" t="inlineStr">
+        <is>
+          <t>category_metrics.accuracy_any</t>
+        </is>
+      </c>
+      <c r="N1" s="3" t="inlineStr">
+        <is>
+          <t>subcategory_metrics.accuracy</t>
+        </is>
+      </c>
+      <c r="O1" s="3" t="inlineStr">
+        <is>
+          <t>subcategory_metrics.precision_macro</t>
+        </is>
+      </c>
+      <c r="P1" s="3" t="inlineStr">
+        <is>
+          <t>subcategory_metrics.recall_macro</t>
+        </is>
+      </c>
+      <c r="Q1" s="3" t="inlineStr">
+        <is>
+          <t>subcategory_metrics.f1_macro</t>
+        </is>
+      </c>
+      <c r="R1" s="3" t="inlineStr">
+        <is>
+          <t>subcategory_metrics.precision_weighted</t>
+        </is>
+      </c>
+      <c r="S1" s="3" t="inlineStr">
+        <is>
+          <t>subcategory_metrics.recall_weighted</t>
+        </is>
+      </c>
+      <c r="T1" s="3" t="inlineStr">
+        <is>
+          <t>subcategory_metrics.f1_weighted</t>
+        </is>
+      </c>
+      <c r="U1" s="3" t="inlineStr">
+        <is>
+          <t>subcategory_metrics.accuracy_any</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>llama3</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>qwen3</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>0</v>
+      </c>
+      <c r="R3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S3" t="n">
+        <v>0</v>
+      </c>
+      <c r="T3" t="n">
+        <v>0</v>
+      </c>
+      <c r="U3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:S3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="3" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
+      <c r="B1" s="3" t="inlineStr">
+        <is>
+          <t>binary_metrics.accuracy</t>
+        </is>
+      </c>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>binary_metrics.precision</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>binary_metrics.recall</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>binary_metrics.f1</t>
+        </is>
+      </c>
+      <c r="F1" s="3" t="inlineStr">
+        <is>
+          <t>category_metrics.accuracy</t>
+        </is>
+      </c>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>category_metrics.precision_macro</t>
+        </is>
+      </c>
+      <c r="H1" s="3" t="inlineStr">
+        <is>
+          <t>category_metrics.recall_macro</t>
+        </is>
+      </c>
+      <c r="I1" s="3" t="inlineStr">
+        <is>
+          <t>category_metrics.f1_macro</t>
+        </is>
+      </c>
+      <c r="J1" s="3" t="inlineStr">
+        <is>
+          <t>category_metrics.precision_weighted</t>
+        </is>
+      </c>
+      <c r="K1" s="3" t="inlineStr">
+        <is>
+          <t>category_metrics.recall_weighted</t>
+        </is>
+      </c>
+      <c r="L1" s="3" t="inlineStr">
+        <is>
+          <t>category_metrics.f1_weighted</t>
+        </is>
+      </c>
+      <c r="M1" s="3" t="inlineStr">
+        <is>
+          <t>subcategory_metrics.accuracy</t>
+        </is>
+      </c>
+      <c r="N1" s="3" t="inlineStr">
+        <is>
+          <t>subcategory_metrics.precision_macro</t>
+        </is>
+      </c>
+      <c r="O1" s="3" t="inlineStr">
+        <is>
+          <t>subcategory_metrics.recall_macro</t>
+        </is>
+      </c>
+      <c r="P1" s="3" t="inlineStr">
+        <is>
+          <t>subcategory_metrics.f1_macro</t>
+        </is>
+      </c>
+      <c r="Q1" s="3" t="inlineStr">
+        <is>
+          <t>subcategory_metrics.precision_weighted</t>
+        </is>
+      </c>
+      <c r="R1" s="3" t="inlineStr">
+        <is>
+          <t>subcategory_metrics.recall_weighted</t>
+        </is>
+      </c>
+      <c r="S1" s="3" t="inlineStr">
+        <is>
+          <t>subcategory_metrics.f1_weighted</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>llama3</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>0.9090909090909091</v>
+      </c>
+      <c r="C2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0.8571428571428571</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.6363636363636364</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.21875</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0.2333333333333333</v>
+      </c>
+      <c r="J2" t="n">
+        <v>0.5568181818181818</v>
+      </c>
+      <c r="K2" t="n">
+        <v>0.6363636363636364</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0.5939393939393939</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="N2" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="O2" t="n">
+        <v>0.08333333333333333</v>
+      </c>
+      <c r="P2" t="n">
+        <v>0.1333333333333333</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>1</v>
+      </c>
+      <c r="R2" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="S2" t="n">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>qwen3</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:S3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="3" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
+      <c r="B1" s="3" t="inlineStr">
+        <is>
+          <t>binary_metrics.accuracy</t>
+        </is>
+      </c>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>binary_metrics.precision</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>binary_metrics.recall</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>binary_metrics.f1</t>
+        </is>
+      </c>
+      <c r="F1" s="3" t="inlineStr">
+        <is>
+          <t>category_metrics.accuracy</t>
+        </is>
+      </c>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>category_metrics.precision_macro</t>
+        </is>
+      </c>
+      <c r="H1" s="3" t="inlineStr">
+        <is>
+          <t>category_metrics.recall_macro</t>
+        </is>
+      </c>
+      <c r="I1" s="3" t="inlineStr">
+        <is>
+          <t>category_metrics.f1_macro</t>
+        </is>
+      </c>
+      <c r="J1" s="3" t="inlineStr">
+        <is>
+          <t>category_metrics.precision_weighted</t>
+        </is>
+      </c>
+      <c r="K1" s="3" t="inlineStr">
+        <is>
+          <t>category_metrics.recall_weighted</t>
+        </is>
+      </c>
+      <c r="L1" s="3" t="inlineStr">
+        <is>
+          <t>category_metrics.f1_weighted</t>
+        </is>
+      </c>
+      <c r="M1" s="3" t="inlineStr">
+        <is>
+          <t>subcategory_metrics.accuracy</t>
+        </is>
+      </c>
+      <c r="N1" s="3" t="inlineStr">
+        <is>
+          <t>subcategory_metrics.precision_macro</t>
+        </is>
+      </c>
+      <c r="O1" s="3" t="inlineStr">
+        <is>
+          <t>subcategory_metrics.recall_macro</t>
+        </is>
+      </c>
+      <c r="P1" s="3" t="inlineStr">
+        <is>
+          <t>subcategory_metrics.f1_macro</t>
+        </is>
+      </c>
+      <c r="Q1" s="3" t="inlineStr">
+        <is>
+          <t>subcategory_metrics.precision_weighted</t>
+        </is>
+      </c>
+      <c r="R1" s="3" t="inlineStr">
+        <is>
+          <t>subcategory_metrics.recall_weighted</t>
+        </is>
+      </c>
+      <c r="S1" s="3" t="inlineStr">
+        <is>
+          <t>subcategory_metrics.f1_weighted</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>llama3</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>0.9090909090909091</v>
+      </c>
+      <c r="C2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0.8571428571428571</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.6363636363636364</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.21875</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0.2333333333333333</v>
+      </c>
+      <c r="J2" t="n">
+        <v>0.5568181818181818</v>
+      </c>
+      <c r="K2" t="n">
+        <v>0.6363636363636364</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0.5939393939393939</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="N2" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="O2" t="n">
+        <v>0.08333333333333333</v>
+      </c>
+      <c r="P2" t="n">
+        <v>0.1333333333333333</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>1</v>
+      </c>
+      <c r="R2" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="S2" t="n">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>qwen3</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:V3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="3" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
+      <c r="B1" s="3" t="inlineStr">
+        <is>
+          <t>binary_metrics.accuracy</t>
+        </is>
+      </c>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>binary_metrics.precision</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>binary_metrics.recall</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>binary_metrics.f1</t>
+        </is>
+      </c>
+      <c r="F1" s="3" t="inlineStr">
+        <is>
+          <t>category_metrics.accuracy</t>
+        </is>
+      </c>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>category_metrics.precision_macro</t>
+        </is>
+      </c>
+      <c r="H1" s="3" t="inlineStr">
+        <is>
+          <t>category_metrics.recall_macro</t>
+        </is>
+      </c>
+      <c r="I1" s="3" t="inlineStr">
+        <is>
+          <t>category_metrics.f1_macro</t>
+        </is>
+      </c>
+      <c r="J1" s="3" t="inlineStr">
+        <is>
+          <t>category_metrics.precision_weighted</t>
+        </is>
+      </c>
+      <c r="K1" s="3" t="inlineStr">
+        <is>
+          <t>category_metrics.recall_weighted</t>
+        </is>
+      </c>
+      <c r="L1" s="3" t="inlineStr">
+        <is>
+          <t>category_metrics.f1_weighted</t>
+        </is>
+      </c>
+      <c r="M1" s="3" t="inlineStr">
+        <is>
+          <t>subcategory_metrics.accuracy</t>
+        </is>
+      </c>
+      <c r="N1" s="3" t="inlineStr">
+        <is>
+          <t>subcategory_metrics.precision_macro</t>
+        </is>
+      </c>
+      <c r="O1" s="3" t="inlineStr">
+        <is>
+          <t>subcategory_metrics.recall_macro</t>
+        </is>
+      </c>
+      <c r="P1" s="3" t="inlineStr">
+        <is>
+          <t>subcategory_metrics.f1_macro</t>
+        </is>
+      </c>
+      <c r="Q1" s="3" t="inlineStr">
+        <is>
+          <t>subcategory_metrics.precision_weighted</t>
+        </is>
+      </c>
+      <c r="R1" s="3" t="inlineStr">
+        <is>
+          <t>subcategory_metrics.recall_weighted</t>
+        </is>
+      </c>
+      <c r="S1" s="3" t="inlineStr">
+        <is>
+          <t>subcategory_metrics.f1_weighted</t>
+        </is>
+      </c>
+      <c r="T1" s="3" t="inlineStr">
+        <is>
+          <t>timing.classify_all_total_s</t>
+        </is>
+      </c>
+      <c r="U1" s="3" t="inlineStr">
+        <is>
+          <t>timing.classify_all_calls</t>
+        </is>
+      </c>
+      <c r="V1" s="3" t="inlineStr">
+        <is>
+          <t>timing.classify_all_avg_ms</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>llama3</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>0.9090909090909091</v>
+      </c>
+      <c r="C2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0.8571428571428571</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.6363636363636364</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.21875</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0.2333333333333333</v>
+      </c>
+      <c r="J2" t="n">
+        <v>0.5568181818181818</v>
+      </c>
+      <c r="K2" t="n">
+        <v>0.6363636363636364</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0.5939393939393939</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="N2" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="O2" t="n">
+        <v>0.08333333333333333</v>
+      </c>
+      <c r="P2" t="n">
+        <v>0.1333333333333333</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>1</v>
+      </c>
+      <c r="R2" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="S2" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="T2" t="n">
+        <v>13.05082559999937</v>
+      </c>
+      <c r="U2" t="n">
+        <v>1</v>
+      </c>
+      <c r="V2" t="n">
+        <v>13050.82559999937</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>qwen3</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr"/>
+      <c r="C3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="O3" t="inlineStr"/>
+      <c r="P3" t="inlineStr"/>
+      <c r="Q3" t="inlineStr"/>
+      <c r="R3" t="inlineStr"/>
+      <c r="S3" t="inlineStr"/>
+      <c r="T3" t="n">
+        <v>26.19365540000035</v>
+      </c>
+      <c r="U3" t="n">
+        <v>1</v>
+      </c>
+      <c r="V3" t="n">
+        <v>26193.65540000035</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>